--- a/galactic_experience/flythrough/series_log.xlsx
+++ b/galactic_experience/flythrough/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,61 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-18 19:09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1789758565057-qfbzxft5vc8.mp4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep03/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/flythrough/series_log.xlsx
+++ b/galactic_experience/flythrough/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,61 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-20 19:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1789930781394-6ks1tdbvtlr.mp4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep04/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/flythrough/series_log.xlsx
+++ b/galactic_experience/flythrough/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,6 +649,116 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-22 19:57</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>744.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1790106721065-wrm47cti73e.mp4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-24 20:09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1790280547881-zz8rnixn5c.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep05/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/flythrough/series_log.xlsx
+++ b/galactic_experience/flythrough/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,61 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1790963890050-lnue29q4rfe.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep06/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/flythrough/series_log.xlsx
+++ b/galactic_experience/flythrough/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,61 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-04 16:56</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1791132912081-xayedsb346s.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep07/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/flythrough/series_log.xlsx
+++ b/galactic_experience/flythrough/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,6 +869,61 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:55</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1791485732990-ptubb0nqa5.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep08/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/flythrough/series_log.xlsx
+++ b/galactic_experience/flythrough/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,61 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 17:25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1791653083201-nanr7u5a0wo.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep09/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/galactic_experience/flythrough/series_log.xlsx
+++ b/galactic_experience/flythrough/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,6 +982,171 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>744.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1791840033403-m95naxbjh0j.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-18 16:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>744.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1792339065665-xza6frrttc.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-24 16:09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1792857693236-qyhdyulame.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/galactic_experience/flythrough/series_log.xlsx
+++ b/galactic_experience/flythrough/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,116 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>744.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1793211954295-xwq4qkw8dr.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>720p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>372.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/seedance/1793383472106-rcps41mdbpg.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flythrough/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
